--- a/backflush_2026-08-19_DAY.xlsx
+++ b/backflush_2026-08-19_DAY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10404"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tmmin.sharepoint.com/sites/DIRECTORATEMANUFACTURING/Shared Documents/03-Division/01-PADSK3/00. SUNTER 1/PAD-02 Logistic &amp; PPC Operation/PPC Engine/01. Daily/08. Data E-Kanban dan BF/WHITE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cal/Documents/Coding/Toyota/toyota-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38FE9CA5-3C36-4781-9D5A-9EA8055C5D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BABFD37-9696-0948-8EB3-63ACB9F67E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="31">
   <si>
     <t>BackFlush Upload</t>
   </si>
@@ -83,9 +83,6 @@
     <t>300</t>
   </si>
   <si>
-    <t>31.07.2026</t>
-  </si>
-  <si>
     <t>1000</t>
   </si>
   <si>
@@ -101,9 +98,6 @@
     <t>D</t>
   </si>
   <si>
-    <t>BF MANUAL PPC WHITE</t>
-  </si>
-  <si>
     <t>114010C060</t>
   </si>
   <si>
@@ -131,25 +125,13 @@
     <t>111010C101</t>
   </si>
   <si>
-    <t>111010C211</t>
-  </si>
-  <si>
-    <t>111010C241</t>
-  </si>
-  <si>
-    <t>111010C012</t>
-  </si>
-  <si>
-    <t>111010C022</t>
-  </si>
-  <si>
-    <t>111010C032</t>
-  </si>
-  <si>
-    <t>111010C042</t>
-  </si>
-  <si>
-    <t>111010C120</t>
+    <t>19.08.2026</t>
+  </si>
+  <si>
+    <t>BF MANUAL CCR WHITE</t>
+  </si>
+  <si>
+    <t>MNL26080042173</t>
   </si>
 </sst>
 </file>
@@ -159,7 +141,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,14 +251,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -600,34 +581,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" customWidth="1"/>
-    <col min="4" max="11" width="18.42578125" customWidth="1"/>
-    <col min="12" max="12" width="24.85546875" customWidth="1"/>
-    <col min="14" max="14" width="29.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" customWidth="1"/>
+    <col min="4" max="11" width="18.5" customWidth="1"/>
+    <col min="12" max="12" width="24.83203125" customWidth="1"/>
+    <col min="14" max="14" width="29.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -641,7 +622,7 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="26.45">
+    <row r="3" spans="1:12" ht="29" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -679,460 +660,365 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>19.08.2026</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>19.08.2026</t>
-        </is>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="10" t="s">
+      <c r="B4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="G4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>114010C090</t>
-        </is>
-      </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="J4" s="6"/>
+      <c r="K4" s="7">
+        <v>62</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="7"/>
-      <c r="K4" s="8">
-        <v>62</v>
-      </c>
-      <c r="L4" s="11" t="inlineStr">
-        <is>
-          <t>BF MANUAL CCR WHITE</t>
-        </is>
+      <c r="H5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="6"/>
+      <c r="K5" s="7">
+        <v>372</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="9" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>19.08.2026</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>19.08.2026</t>
-        </is>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="10" t="s">
+      <c r="B6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>114010C060</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="s">
+      <c r="G6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="7"/>
-      <c r="K5" s="8">
-        <v>372</v>
-      </c>
-      <c r="L5" s="11" t="inlineStr">
-        <is>
-          <t>BF MANUAL CCR WHITE</t>
-        </is>
+      <c r="J6" s="6"/>
+      <c r="K6" s="7">
+        <v>50</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="9" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>19.08.2026</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>19.08.2026</t>
-        </is>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="10" t="s">
+      <c r="B7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>134010C030</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="s">
+      <c r="G7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="7"/>
-      <c r="K6" s="8">
-        <v>50</v>
-      </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>BF MANUAL CCR WHITE</t>
-        </is>
+      <c r="J7" s="6"/>
+      <c r="K7" s="7">
+        <v>387</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="9" t="s">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>19.08.2026</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>19.08.2026</t>
-        </is>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="10" t="s">
+      <c r="B8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>134010C022</t>
-        </is>
-      </c>
-      <c r="H7" s="10" t="s">
+      <c r="G8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="7"/>
-      <c r="K7" s="8">
-        <v>387</v>
-      </c>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>BF MANUAL CCR WHITE</t>
-        </is>
+      <c r="J8" s="6"/>
+      <c r="K8" s="7">
+        <v>331</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="9" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>19.08.2026</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>19.08.2026</t>
-        </is>
-      </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="10" t="s">
+      <c r="B9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>135010C011</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="s">
+      <c r="G9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" s="7"/>
-      <c r="K8" s="8">
+      <c r="J9" s="6"/>
+      <c r="K9" s="7">
         <v>331</v>
       </c>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>BF MANUAL CCR WHITE</t>
-        </is>
+      <c r="L9" s="10" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="9" t="s">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>19.08.2026</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>19.08.2026</t>
-        </is>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="10" t="s">
+      <c r="B10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>135020C030</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="s">
+      <c r="G10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="7"/>
-      <c r="K9" s="8">
-        <v>331</v>
-      </c>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>BF MANUAL CCR WHITE</t>
-        </is>
+      <c r="J10" s="6"/>
+      <c r="K10" s="7">
+        <v>11</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="9" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>19.08.2026</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>19.08.2026</t>
-        </is>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="10" t="s">
+      <c r="B11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>111010C091</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="s">
+      <c r="G11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" s="7"/>
-      <c r="K10" s="8">
-        <v>11</v>
-      </c>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>BF MANUAL CCR WHITE</t>
-        </is>
+      <c r="J11" s="6"/>
+      <c r="K11" s="7">
+        <v>34</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="9" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>19.08.2026</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>19.08.2026</t>
-        </is>
-      </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="10" t="s">
+      <c r="B12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>111010C081</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="s">
+      <c r="G12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" s="7"/>
-      <c r="K11" s="8">
-        <v>34</v>
-      </c>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>BF MANUAL CCR WHITE</t>
-        </is>
+      <c r="J12" s="6"/>
+      <c r="K12" s="7">
+        <v>94</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="9" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>19.08.2026</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>19.08.2026</t>
-        </is>
-      </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="10" t="s">
+      <c r="B13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>111010C111</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="s">
+      <c r="G13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I12" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J12" s="7"/>
-      <c r="K12" s="8">
-        <v>94</v>
-      </c>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>BF MANUAL CCR WHITE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>19.08.2026</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>19.08.2026</t>
-        </is>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>111010C101</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J13" s="7"/>
-      <c r="K13" s="8">
+      <c r="J13" s="6"/>
+      <c r="K13" s="7">
         <v>283</v>
       </c>
-      <c r="L13" s="11" t="inlineStr">
-        <is>
-          <t>BF MANUAL CCR WHITE</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" spans="1:12"/>
-    <row r="15" spans="1:12"/>
-    <row r="16" spans="1:12"/>
-    <row r="17" spans="1:12"/>
-    <row r="18" spans="1:12"/>
-    <row r="19" spans="1:12"/>
-    <row r="20" spans="1:12"/>
-    <row r="21" spans="1:12">
-      <c r="A21" s="4"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="7"/>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" s="4"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="7"/>
+      <c r="L13" s="10" t="s">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1154,6 +1040,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="505c0d7f-1821-429e-911e-d66f56e269d7" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fa86a8e1-0a51-4d2b-89d8-f347c4e836f4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C40E32B3BC6C0943846CC9A8544019F2" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3945682fd4a0af0f289abdd346dec685">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="505c0d7f-1821-429e-911e-d66f56e269d7" xmlns:ns3="fa86a8e1-0a51-4d2b-89d8-f347c4e836f4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7efa866925d47ca17c8d4de6dd169f29" ns2:_="" ns3:_="">
     <xsd:import namespace="505c0d7f-1821-429e-911e-d66f56e269d7"/>
@@ -1414,25 +1311,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="505c0d7f-1821-429e-911e-d66f56e269d7" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fa86a8e1-0a51-4d2b-89d8-f347c4e836f4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB35FE7D-EE20-43B2-828E-9E83EACD02ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB35FE7D-EE20-43B2-828E-9E83EACD02ED}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{608D8CD9-163C-4FD7-B869-0ED7D20A686D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FE50C4C-C24F-4528-B1FB-AAD92F27FE5C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="505c0d7f-1821-429e-911e-d66f56e269d7"/>
+    <ds:schemaRef ds:uri="fa86a8e1-0a51-4d2b-89d8-f347c4e836f4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FE50C4C-C24F-4528-B1FB-AAD92F27FE5C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{608D8CD9-163C-4FD7-B869-0ED7D20A686D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="505c0d7f-1821-429e-911e-d66f56e269d7"/>
+    <ds:schemaRef ds:uri="fa86a8e1-0a51-4d2b-89d8-f347c4e836f4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/backflush_2026-08-19_DAY.xlsx
+++ b/backflush_2026-08-19_DAY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30404"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cal/Documents/Coding/Toyota/toyota-ccr/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tmmin.sharepoint.com/sites/DIRECTORATEMANUFACTURING/Shared Documents/03-Division/01-PADSK3/00. SUNTER 1/PAD-02 Logistic &amp; PPC Operation/PPC Engine/01. Daily/08. Data E-Kanban dan BF/WHITE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BABFD37-9696-0948-8EB3-63ACB9F67E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{38FE9CA5-3C36-4781-9D5A-9EA8055C5D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="37">
   <si>
     <t>BackFlush Upload</t>
   </si>
@@ -83,6 +83,9 @@
     <t>300</t>
   </si>
   <si>
+    <t>31.07.2026</t>
+  </si>
+  <si>
     <t>1000</t>
   </si>
   <si>
@@ -98,6 +101,9 @@
     <t>D</t>
   </si>
   <si>
+    <t>BF MANUAL PPC WHITE</t>
+  </si>
+  <si>
     <t>114010C060</t>
   </si>
   <si>
@@ -125,13 +131,25 @@
     <t>111010C101</t>
   </si>
   <si>
-    <t>19.08.2026</t>
-  </si>
-  <si>
-    <t>BF MANUAL CCR WHITE</t>
-  </si>
-  <si>
-    <t>MNL26080042173</t>
+    <t>111010C211</t>
+  </si>
+  <si>
+    <t>111010C241</t>
+  </si>
+  <si>
+    <t>111010C012</t>
+  </si>
+  <si>
+    <t>111010C022</t>
+  </si>
+  <si>
+    <t>111010C032</t>
+  </si>
+  <si>
+    <t>111010C042</t>
+  </si>
+  <si>
+    <t>111010C120</t>
   </si>
 </sst>
 </file>
@@ -141,7 +159,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -251,13 +269,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -582,33 +601,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:L13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" customWidth="1"/>
-    <col min="4" max="11" width="18.5" customWidth="1"/>
-    <col min="12" max="12" width="24.83203125" customWidth="1"/>
-    <col min="14" max="14" width="29.6640625" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="4" max="11" width="18.42578125" customWidth="1"/>
+    <col min="12" max="12" width="24.85546875" customWidth="1"/>
+    <col min="14" max="14" width="29.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -622,7 +641,7 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="29" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="26.45">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -660,364 +679,424 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:12">
+      <c r="A4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="10" t="s">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="F4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="10" t="s">
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>114010C090</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="7">
+      <c r="I4" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="7"/>
+      <c r="K4" s="8">
         <v>62</v>
       </c>
-      <c r="L4" s="10" t="s">
-        <v>29</v>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>BF MANUAL CCR WHITE</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:12">
+      <c r="A5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="10" t="s">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="F5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>114010C060</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="10" t="s">
+      <c r="J5" s="7"/>
+      <c r="K5" s="8">
+        <v>372</v>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>BF MANUAL CCR WHITE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>134010C030</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="6"/>
-      <c r="K5" s="7">
-        <v>372</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>29</v>
+      <c r="I6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="7"/>
+      <c r="K6" s="8">
+        <v>50</v>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>BF MANUAL CCR WHITE</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
+    <row r="7" spans="1:12">
+      <c r="A7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="10" t="s">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="10" t="s">
+      <c r="F7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>134010C022</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="6"/>
-      <c r="K6" s="7">
-        <v>50</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>29</v>
+      <c r="I7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="7"/>
+      <c r="K7" s="8">
+        <v>387</v>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>BF MANUAL CCR WHITE</t>
+        </is>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
+    <row r="8" spans="1:12">
+      <c r="A8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="10" t="s">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="10" t="s">
+      <c r="F8" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>135010C011</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="6"/>
-      <c r="K7" s="7">
-        <v>387</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>29</v>
+      <c r="I8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="7"/>
+      <c r="K8" s="8">
+        <v>331</v>
+      </c>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>BF MANUAL CCR WHITE</t>
+        </is>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
+    <row r="9" spans="1:12">
+      <c r="A9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="10" t="s">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="10" t="s">
+      <c r="F9" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>135020C030</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J8" s="6"/>
-      <c r="K8" s="7">
+      <c r="I9" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="7"/>
+      <c r="K9" s="8">
         <v>331</v>
       </c>
-      <c r="L8" s="10" t="s">
-        <v>29</v>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>BF MANUAL CCR WHITE</t>
+        </is>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
+    <row r="10" spans="1:12">
+      <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="10" t="s">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="10" t="s">
+      <c r="F10" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>111010C091</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="6"/>
-      <c r="K9" s="7">
-        <v>331</v>
-      </c>
-      <c r="L9" s="10" t="s">
-        <v>29</v>
+      <c r="I10" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="7"/>
+      <c r="K10" s="8">
+        <v>11</v>
+      </c>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>BF MANUAL CCR WHITE</t>
+        </is>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
+    <row r="11" spans="1:12">
+      <c r="A11" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="10" t="s">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="10" t="s">
+      <c r="F11" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>111010C081</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="6"/>
-      <c r="K10" s="7">
-        <v>11</v>
-      </c>
-      <c r="L10" s="10" t="s">
-        <v>29</v>
+      <c r="I11" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="7"/>
+      <c r="K11" s="8">
+        <v>34</v>
+      </c>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>BF MANUAL CCR WHITE</t>
+        </is>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="8" t="s">
+    <row r="12" spans="1:12">
+      <c r="A12" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="10" t="s">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="10" t="s">
+      <c r="F12" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>111010C111</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J11" s="6"/>
-      <c r="K11" s="7">
-        <v>34</v>
-      </c>
-      <c r="L11" s="10" t="s">
-        <v>29</v>
+      <c r="I12" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="7"/>
+      <c r="K12" s="8">
+        <v>94</v>
+      </c>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>BF MANUAL CCR WHITE</t>
+        </is>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
+    <row r="13" spans="1:12">
+      <c r="A13" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="10" t="s">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="10" t="s">
+      <c r="F13" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>111010C101</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J12" s="6"/>
-      <c r="K12" s="7">
-        <v>94</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" s="6"/>
-      <c r="K13" s="7">
+      <c r="I13" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="7"/>
+      <c r="K13" s="8">
         <v>283</v>
       </c>
-      <c r="L13" s="10" t="s">
-        <v>29</v>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>BF MANUAL CCR WHITE</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1040,17 +1119,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="505c0d7f-1821-429e-911e-d66f56e269d7" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fa86a8e1-0a51-4d2b-89d8-f347c4e836f4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C40E32B3BC6C0943846CC9A8544019F2" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3945682fd4a0af0f289abdd346dec685">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="505c0d7f-1821-429e-911e-d66f56e269d7" xmlns:ns3="fa86a8e1-0a51-4d2b-89d8-f347c4e836f4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7efa866925d47ca17c8d4de6dd169f29" ns2:_="" ns3:_="">
     <xsd:import namespace="505c0d7f-1821-429e-911e-d66f56e269d7"/>
@@ -1311,40 +1379,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="505c0d7f-1821-429e-911e-d66f56e269d7" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fa86a8e1-0a51-4d2b-89d8-f347c4e836f4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB35FE7D-EE20-43B2-828E-9E83EACD02ED}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB35FE7D-EE20-43B2-828E-9E83EACD02ED}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FE50C4C-C24F-4528-B1FB-AAD92F27FE5C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="505c0d7f-1821-429e-911e-d66f56e269d7"/>
-    <ds:schemaRef ds:uri="fa86a8e1-0a51-4d2b-89d8-f347c4e836f4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{608D8CD9-163C-4FD7-B869-0ED7D20A686D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{608D8CD9-163C-4FD7-B869-0ED7D20A686D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="505c0d7f-1821-429e-911e-d66f56e269d7"/>
-    <ds:schemaRef ds:uri="fa86a8e1-0a51-4d2b-89d8-f347c4e836f4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FE50C4C-C24F-4528-B1FB-AAD92F27FE5C}"/>
 </file>